--- a/demo/dynamic_02.xlsx
+++ b/demo/dynamic_02.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\William\Documents\GitHub\PyVBAai\demo\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20160E3-139E-4427-B4C8-252F90AEDA4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="8680" yWindow="1880" windowWidth="31220" windowHeight="18030" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="7910" yWindow="2460" windowWidth="31220" windowHeight="18030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -48,63 +54,136 @@
 </metadata>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>FILTER: Fruit rows</t>
+  </si>
+  <si>
+    <t>XLOOKUP: Apple sales</t>
+  </si>
+  <si>
+    <t>UNIQUE: Categories</t>
+  </si>
+  <si>
+    <t>SORT: Items A-Z</t>
+  </si>
+  <si>
+    <t>SEQUENCE: 5x3</t>
+  </si>
+  <si>
+    <t>Fruit</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>Banana</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>Carrot</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Broccoli</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <b val="1"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="8">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="FFEADCF8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EADCF8"/>
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -116,89 +195,106 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="7">
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="7" tint="-0.249977111117893"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="DataTable" displayName="DataTable" ref="A1:D7" headerRowDxfId="2" dataDxfId="0" totalsRowDxfId="1">
+  <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Category" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Item" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Region" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Sales" dataDxfId="3"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -517,263 +613,286 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S7"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col min="1" max="17" width="14" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Region</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Sales</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>FILTER: Fruit rows</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>XLOOKUP: Apple sales</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>UNIQUE: Categories</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>SORT: Items A-Z</t>
-        </is>
-      </c>
-      <c r="Q1" s="2" t="inlineStr">
-        <is>
-          <t>SEQUENCE: 5x3</t>
-        </is>
+    <row r="1" spans="1:19">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Fruit</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="2" spans="1:19">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2">
         <v>120</v>
       </c>
-      <c r="F2" s="3" cm="1">
-        <f t="array" ref="F2">_xlfn.FILTER(A2:D7,A2:A7="Fruit","No matches")</f>
-        <v/>
-      </c>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="K2" s="4" cm="1">
-        <f t="array" ref="K2">_xlfn.XLOOKUP("Apple",B2:B7,D2:D7,"Not found")</f>
-        <v/>
-      </c>
-      <c r="M2" s="5" cm="1">
-        <f t="array" ref="M2">_xlfn.UNIQUE(A2:A7)</f>
-        <v/>
-      </c>
-      <c r="O2" s="6" cm="1">
-        <f t="array" ref="O2">_xlfn.SORT(B2:B7)</f>
-        <v/>
-      </c>
-      <c r="Q2" s="7" cm="1">
-        <f t="array" ref="Q2">_xlfn.SEQUENCE(5,3,1,1)</f>
-        <v/>
+      <c r="F2" s="4" t="str" cm="1">
+        <f t="array" ref="F2:I5">_xlfn._xlws.FILTER(DataTable[#Data],DataTable[Category]="Fruit","No matches")</f>
+        <v>Fruit</v>
+      </c>
+      <c r="G2" s="4" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="H2" s="4" t="str">
+        <v>East</v>
+      </c>
+      <c r="I2" s="4">
+        <v>120</v>
+      </c>
+      <c r="K2" s="5" cm="1">
+        <f t="array" ref="K2:K7">_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(O2),DataTable[Item],DataTable[Sales],"Not found")</f>
+        <v>120</v>
+      </c>
+      <c r="M2" s="6" t="str" cm="1">
+        <f t="array" ref="M2:M3">_xlfn.UNIQUE(DataTable[Category])</f>
+        <v>Fruit</v>
+      </c>
+      <c r="O2" s="7" t="str" cm="1">
+        <f t="array" ref="O2:O7">_xlfn._xlws.SORT(DataTable[Item])</f>
+        <v>Apple</v>
+      </c>
+      <c r="Q2" s="8" cm="1">
+        <f t="array" ref="Q2:S6">_xlfn.SEQUENCE(5,3,1,1)</f>
+        <v>1</v>
+      </c>
+      <c r="R2" s="8">
+        <v>2</v>
+      </c>
+      <c r="S2" s="8">
+        <v>3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Fruit</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Banana</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:19">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2">
         <v>95</v>
       </c>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="M3" s="5" t="n"/>
-      <c r="O3" s="6" t="n"/>
-      <c r="Q3" s="7" t="n"/>
+      <c r="F3" s="9" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="G3" s="9" t="str">
+        <v>Banana</v>
+      </c>
+      <c r="H3" s="9" t="str">
+        <v>West</v>
+      </c>
+      <c r="I3" s="9">
+        <v>95</v>
+      </c>
+      <c r="K3" s="10">
+        <v>120</v>
+      </c>
+      <c r="M3" s="11" t="str">
+        <v>Vegetable</v>
+      </c>
+      <c r="O3" s="12" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="Q3" s="13">
+        <v>4</v>
+      </c>
+      <c r="R3" s="13">
+        <v>5</v>
+      </c>
+      <c r="S3" s="13">
+        <v>6</v>
+      </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Vegetable</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Carrot</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:19">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="2">
         <v>80</v>
       </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="M4" s="5" t="n"/>
-      <c r="O4" s="6" t="n"/>
-      <c r="Q4" s="7" t="n"/>
+      <c r="F4" s="9" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="G4" s="9" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="H4" s="9" t="str">
+        <v>North</v>
+      </c>
+      <c r="I4" s="9">
+        <v>110</v>
+      </c>
+      <c r="K4" s="10">
+        <v>95</v>
+      </c>
+      <c r="M4" s="11"/>
+      <c r="O4" s="12" t="str">
+        <v>Banana</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>7</v>
+      </c>
+      <c r="R4" s="13">
+        <v>8</v>
+      </c>
+      <c r="S4" s="13">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Fruit</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+    <row r="5" spans="1:19">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="2">
         <v>110</v>
       </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="O5" s="6" t="n"/>
-      <c r="Q5" s="7" t="n"/>
+      <c r="F5" s="9" t="str">
+        <v>Fruit</v>
+      </c>
+      <c r="G5" s="9" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="H5" s="9" t="str">
+        <v>East</v>
+      </c>
+      <c r="I5" s="9">
+        <v>105</v>
+      </c>
+      <c r="K5" s="10">
+        <v>130</v>
+      </c>
+      <c r="M5" s="11"/>
+      <c r="O5" s="12" t="str">
+        <v>Broccoli</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>10</v>
+      </c>
+      <c r="R5" s="13">
+        <v>11</v>
+      </c>
+      <c r="S5" s="13">
+        <v>12</v>
+      </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Vegetable</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Broccoli</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>West</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    <row r="6" spans="1:19">
+      <c r="A6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2">
         <v>130</v>
       </c>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="O6" s="6" t="n"/>
-      <c r="Q6" s="7" t="n"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="K6" s="10">
+        <v>80</v>
+      </c>
+      <c r="M6" s="11"/>
+      <c r="O6" s="12" t="str">
+        <v>Carrot</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>13</v>
+      </c>
+      <c r="R6" s="13">
+        <v>14</v>
+      </c>
+      <c r="S6" s="13">
+        <v>15</v>
+      </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Fruit</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Orange</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>East</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
+    <row r="7" spans="1:19">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="2">
         <v>105</v>
       </c>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="O7" s="6" t="n"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="9"/>
+      <c r="I7" s="9"/>
+      <c r="K7" s="10">
+        <v>105</v>
+      </c>
+      <c r="M7" s="11"/>
+      <c r="O7" s="12" t="str">
+        <v>Orange</v>
+      </c>
+      <c r="Q7" s="14"/>
+      <c r="R7" s="14"/>
+      <c r="S7" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>